--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Minor.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Minor.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>Source</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -387,10 +390,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,6 +435,9 @@
       </c>
       <c r="N1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Minor.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Minor.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -440,6 +440,1127 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" spans="1:15">
+      <c r="A2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4">
+        <f t="shared" ref="A4:A67" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <f t="shared" ref="A68:A131" si="1">A67+1</f>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <f t="shared" si="1"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <f t="shared" si="1"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <f t="shared" si="1"/>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <f t="shared" si="1"/>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <f t="shared" si="1"/>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <f t="shared" si="1"/>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <f t="shared" si="1"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <f t="shared" si="1"/>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <f t="shared" si="1"/>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <f t="shared" si="1"/>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <f t="shared" si="1"/>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <f t="shared" ref="A132:A188" si="2">A131+1</f>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <f t="shared" si="2"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <f t="shared" si="2"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <f t="shared" si="2"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <f t="shared" si="2"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <f t="shared" si="2"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <f t="shared" si="2"/>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <f t="shared" si="2"/>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <f t="shared" si="2"/>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <f t="shared" si="2"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <f t="shared" si="2"/>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <f t="shared" si="2"/>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <f t="shared" si="2"/>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <f t="shared" si="2"/>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <f t="shared" si="2"/>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <f t="shared" si="2"/>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <f t="shared" si="2"/>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <f t="shared" si="2"/>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <f t="shared" si="2"/>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <f t="shared" si="2"/>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <f t="shared" si="2"/>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <f t="shared" si="2"/>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <f t="shared" si="2"/>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <f t="shared" si="2"/>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <f t="shared" si="2"/>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <f t="shared" si="2"/>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <f t="shared" si="2"/>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <f t="shared" si="2"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <f t="shared" si="2"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <f t="shared" si="2"/>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <f t="shared" si="2"/>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <f t="shared" si="2"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <f t="shared" si="2"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <f t="shared" si="2"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <f t="shared" si="2"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <f t="shared" si="2"/>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <f t="shared" si="2"/>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <f t="shared" si="2"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <f t="shared" si="2"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <f t="shared" si="2"/>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <f t="shared" si="2"/>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <f t="shared" si="2"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <f t="shared" si="2"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <f t="shared" si="2"/>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <f t="shared" si="2"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <f t="shared" si="2"/>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <f t="shared" si="2"/>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <f t="shared" si="2"/>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <f t="shared" si="2"/>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <f t="shared" si="2"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <f t="shared" si="2"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <f t="shared" si="2"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <f t="shared" si="2"/>
+        <v>187</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Minor.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Minor.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="20">
   <si>
     <t>ID</t>
   </si>
@@ -59,6 +59,21 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Mississippi Choctaw</t>
+  </si>
+  <si>
+    <t>Mississippi Blood Minor</t>
+  </si>
+  <si>
+    <t>Dawes Rolls Full Document - Choctaw By Blood - Page 168</t>
+  </si>
+  <si>
+    <t>Dawes Rolls Full Document - Choctaw By Blood - Page 169</t>
+  </si>
+  <si>
+    <t>Dawes Rolls Full Document - Choctaw By Blood - Page 170</t>
   </si>
 </sst>
 </file>
@@ -392,6 +407,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O188"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="12" max="12" width="24.85546875" customWidth="1"/>
+    <col min="14" max="14" width="57.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
@@ -444,1121 +464,3733 @@
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>168</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <f>C2</f>
+        <v>168</v>
+      </c>
+      <c r="L3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="str">
+        <f>N2</f>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:C12" si="1">C3</f>
+        <v>168</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" t="str">
+        <f t="shared" ref="N4:N12" si="2">N3</f>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="1"/>
+        <v>168</v>
+      </c>
+      <c r="L5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" t="str">
+        <f t="shared" si="2"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>168</v>
+      </c>
+      <c r="L6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" t="str">
+        <f t="shared" si="2"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>168</v>
+      </c>
+      <c r="L7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" si="2"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>168</v>
+      </c>
+      <c r="L8" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" t="str">
+        <f t="shared" si="2"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>168</v>
+      </c>
+      <c r="L9" t="s">
+        <v>16</v>
+      </c>
+      <c r="N9" t="str">
+        <f t="shared" si="2"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>168</v>
+      </c>
+      <c r="L10" t="s">
+        <v>16</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="2"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="1"/>
+        <v>168</v>
+      </c>
+      <c r="L11" t="s">
+        <v>16</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="2"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="1"/>
+        <v>168</v>
+      </c>
+      <c r="L12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N12" t="str">
+        <f t="shared" si="2"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>169</v>
+      </c>
+      <c r="L13" t="s">
+        <v>16</v>
+      </c>
+      <c r="N13" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14">
+        <f>C13</f>
+        <v>169</v>
+      </c>
+      <c r="L14" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" t="str">
+        <f>N13</f>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:C78" si="3">C14</f>
+        <v>169</v>
+      </c>
+      <c r="L15" t="s">
+        <v>16</v>
+      </c>
+      <c r="N15" t="str">
+        <f t="shared" ref="N15:N78" si="4">N14</f>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L16" t="s">
+        <v>16</v>
+      </c>
+      <c r="N16" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L17" t="s">
+        <v>16</v>
+      </c>
+      <c r="N17" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L18" t="s">
+        <v>16</v>
+      </c>
+      <c r="N18" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L19" t="s">
+        <v>16</v>
+      </c>
+      <c r="N19" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L20" t="s">
+        <v>16</v>
+      </c>
+      <c r="N20" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L21" t="s">
+        <v>16</v>
+      </c>
+      <c r="N21" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L22" t="s">
+        <v>16</v>
+      </c>
+      <c r="N22" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L23" t="s">
+        <v>16</v>
+      </c>
+      <c r="N23" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
+      <c r="B24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L24" t="s">
+        <v>16</v>
+      </c>
+      <c r="N24" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1">
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L25" t="s">
+        <v>16</v>
+      </c>
+      <c r="N25" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:1">
+      <c r="B26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L26" t="s">
+        <v>16</v>
+      </c>
+      <c r="N26" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1">
+      <c r="B27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L27" t="s">
+        <v>16</v>
+      </c>
+      <c r="N27" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L28" t="s">
+        <v>16</v>
+      </c>
+      <c r="N28" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:1">
+      <c r="B29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L29" t="s">
+        <v>16</v>
+      </c>
+      <c r="N29" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:1">
+      <c r="B30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L30" t="s">
+        <v>16</v>
+      </c>
+      <c r="N30" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:1">
+      <c r="B31" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L31" t="s">
+        <v>16</v>
+      </c>
+      <c r="N31" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L32" t="s">
+        <v>16</v>
+      </c>
+      <c r="N32" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L33" t="s">
+        <v>16</v>
+      </c>
+      <c r="N33" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L34" t="s">
+        <v>16</v>
+      </c>
+      <c r="N34" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L35" t="s">
+        <v>16</v>
+      </c>
+      <c r="N35" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L36" t="s">
+        <v>16</v>
+      </c>
+      <c r="N36" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L37" t="s">
+        <v>16</v>
+      </c>
+      <c r="N37" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L38" t="s">
+        <v>16</v>
+      </c>
+      <c r="N38" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L39" t="s">
+        <v>16</v>
+      </c>
+      <c r="N39" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L40" t="s">
+        <v>16</v>
+      </c>
+      <c r="N40" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L41" t="s">
+        <v>16</v>
+      </c>
+      <c r="N41" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
+      <c r="B42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L42" t="s">
+        <v>16</v>
+      </c>
+      <c r="N42" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:1">
+      <c r="B43" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L43" t="s">
+        <v>16</v>
+      </c>
+      <c r="N43" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:1">
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L44" t="s">
+        <v>16</v>
+      </c>
+      <c r="N44" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:1">
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L45" t="s">
+        <v>16</v>
+      </c>
+      <c r="N45" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:1">
+      <c r="B46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L46" t="s">
+        <v>16</v>
+      </c>
+      <c r="N46" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:1">
+      <c r="B47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L47" t="s">
+        <v>16</v>
+      </c>
+      <c r="N47" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L48" t="s">
+        <v>16</v>
+      </c>
+      <c r="N48" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L49" t="s">
+        <v>16</v>
+      </c>
+      <c r="N49" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="B50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L50" t="s">
+        <v>16</v>
+      </c>
+      <c r="N50" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
+      <c r="B51" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L51" t="s">
+        <v>16</v>
+      </c>
+      <c r="N51" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="B52" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L52" t="s">
+        <v>16</v>
+      </c>
+      <c r="N52" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L53" t="s">
+        <v>16</v>
+      </c>
+      <c r="N53" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:1">
+      <c r="B54" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L54" t="s">
+        <v>16</v>
+      </c>
+      <c r="N54" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:1">
+      <c r="B55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L55" t="s">
+        <v>16</v>
+      </c>
+      <c r="N55" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:1">
+      <c r="B56" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L56" t="s">
+        <v>16</v>
+      </c>
+      <c r="N56" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:1">
+      <c r="B57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L57" t="s">
+        <v>16</v>
+      </c>
+      <c r="N57" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="1:1">
+      <c r="B58" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L58" t="s">
+        <v>16</v>
+      </c>
+      <c r="N58" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="1:1">
+      <c r="B59" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L59" t="s">
+        <v>16</v>
+      </c>
+      <c r="N59" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:1">
+      <c r="B60" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L60" t="s">
+        <v>16</v>
+      </c>
+      <c r="N60" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:1">
+      <c r="B61" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L61" t="s">
+        <v>16</v>
+      </c>
+      <c r="N61" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:1">
+      <c r="B62" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L62" t="s">
+        <v>16</v>
+      </c>
+      <c r="N62" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="1:1">
+      <c r="B63" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L63" t="s">
+        <v>16</v>
+      </c>
+      <c r="N63" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
+      <c r="B64" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L64" t="s">
+        <v>16</v>
+      </c>
+      <c r="N64" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L65" t="s">
+        <v>16</v>
+      </c>
+      <c r="N65" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:1">
+      <c r="B66" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L66" t="s">
+        <v>16</v>
+      </c>
+      <c r="N66" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:1">
+      <c r="B67" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L67" t="s">
+        <v>16</v>
+      </c>
+      <c r="N67" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
       <c r="A68">
-        <f t="shared" ref="A68:A131" si="1">A67+1</f>
+        <f t="shared" ref="A68:A131" si="5">A67+1</f>
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:1">
+      <c r="B68" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L68" t="s">
+        <v>16</v>
+      </c>
+      <c r="N68" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
       <c r="A69">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:1">
+      <c r="B69" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L69" t="s">
+        <v>16</v>
+      </c>
+      <c r="N69" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:1">
+      <c r="B70" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N70" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
       <c r="A71">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:1">
+      <c r="B71" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L71" t="s">
+        <v>16</v>
+      </c>
+      <c r="N71" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
       <c r="A72">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:1">
+      <c r="B72" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L72" t="s">
+        <v>16</v>
+      </c>
+      <c r="N72" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
       <c r="A73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:1">
+      <c r="B73" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L73" t="s">
+        <v>16</v>
+      </c>
+      <c r="N73" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
       <c r="A74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:1">
+      <c r="B74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L74" t="s">
+        <v>16</v>
+      </c>
+      <c r="N74" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
       <c r="A75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:1">
+      <c r="B75" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L75" t="s">
+        <v>16</v>
+      </c>
+      <c r="N75" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
       <c r="A76">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:1">
+      <c r="B76" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L76" t="s">
+        <v>16</v>
+      </c>
+      <c r="N76" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
       <c r="A77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:1">
+      <c r="B77" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L77" t="s">
+        <v>16</v>
+      </c>
+      <c r="N77" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
       <c r="A78">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:1">
+      <c r="B78" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="L78" t="s">
+        <v>16</v>
+      </c>
+      <c r="N78" t="str">
+        <f t="shared" si="4"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
       <c r="A79">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:1">
+      <c r="B79" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79">
+        <f t="shared" ref="C79:C142" si="6">C78</f>
+        <v>169</v>
+      </c>
+      <c r="L79" t="s">
+        <v>16</v>
+      </c>
+      <c r="N79" t="str">
+        <f t="shared" ref="N79:N142" si="7">N78</f>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
       <c r="A80">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:1">
+      <c r="B80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L80" t="s">
+        <v>16</v>
+      </c>
+      <c r="N80" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
       <c r="A81">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:1">
+      <c r="B81" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L81" t="s">
+        <v>16</v>
+      </c>
+      <c r="N81" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
       <c r="A82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:1">
+      <c r="B82" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L82" t="s">
+        <v>16</v>
+      </c>
+      <c r="N82" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
       <c r="A83">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:1">
+      <c r="B83" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L83" t="s">
+        <v>16</v>
+      </c>
+      <c r="N83" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
       <c r="A84">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:1">
+      <c r="B84" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L84" t="s">
+        <v>16</v>
+      </c>
+      <c r="N84" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
       <c r="A85">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:1">
+      <c r="B85" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L85" t="s">
+        <v>16</v>
+      </c>
+      <c r="N85" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
       <c r="A86">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:1">
+      <c r="B86" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L86" t="s">
+        <v>16</v>
+      </c>
+      <c r="N86" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
       <c r="A87">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:1">
+      <c r="B87" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L87" t="s">
+        <v>16</v>
+      </c>
+      <c r="N87" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
       <c r="A88">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:1">
+      <c r="B88" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L88" t="s">
+        <v>16</v>
+      </c>
+      <c r="N88" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
       <c r="A89">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:1">
+      <c r="B89" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L89" t="s">
+        <v>16</v>
+      </c>
+      <c r="N89" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
       <c r="A90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:1">
+      <c r="B90" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L90" t="s">
+        <v>16</v>
+      </c>
+      <c r="N90" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
       <c r="A91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>90</v>
       </c>
-    </row>
-    <row r="92" spans="1:1">
+      <c r="B91" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L91" t="s">
+        <v>16</v>
+      </c>
+      <c r="N91" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
       <c r="A92">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>91</v>
       </c>
-    </row>
-    <row r="93" spans="1:1">
+      <c r="B92" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L92" t="s">
+        <v>16</v>
+      </c>
+      <c r="N92" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14">
       <c r="A93">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:1">
+      <c r="B93" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L93" t="s">
+        <v>16</v>
+      </c>
+      <c r="N93" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
       <c r="A94">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:1">
+      <c r="B94" t="s">
+        <v>15</v>
+      </c>
+      <c r="C94">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L94" t="s">
+        <v>16</v>
+      </c>
+      <c r="N94" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
       <c r="A95">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>94</v>
       </c>
-    </row>
-    <row r="96" spans="1:1">
+      <c r="B95" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L95" t="s">
+        <v>16</v>
+      </c>
+      <c r="N95" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
       <c r="A96">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
+      <c r="B96" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L96" t="s">
+        <v>16</v>
+      </c>
+      <c r="N96" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
       <c r="A97">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
+      <c r="B97" t="s">
+        <v>15</v>
+      </c>
+      <c r="C97">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L97" t="s">
+        <v>16</v>
+      </c>
+      <c r="N97" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
       <c r="A98">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:1">
+      <c r="B98" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L98" t="s">
+        <v>16</v>
+      </c>
+      <c r="N98" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
       <c r="A99">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:1">
+      <c r="B99" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L99" t="s">
+        <v>16</v>
+      </c>
+      <c r="N99" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14">
       <c r="A100">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:1">
+      <c r="B100" t="s">
+        <v>15</v>
+      </c>
+      <c r="C100">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L100" t="s">
+        <v>16</v>
+      </c>
+      <c r="N100" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14">
       <c r="A101">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
-    </row>
-    <row r="102" spans="1:1">
+      <c r="B101" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L101" t="s">
+        <v>16</v>
+      </c>
+      <c r="N101" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
       <c r="A102">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>101</v>
       </c>
-    </row>
-    <row r="103" spans="1:1">
+      <c r="B102" t="s">
+        <v>15</v>
+      </c>
+      <c r="C102">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L102" t="s">
+        <v>16</v>
+      </c>
+      <c r="N102" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
       <c r="A103">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>102</v>
       </c>
-    </row>
-    <row r="104" spans="1:1">
+      <c r="B103" t="s">
+        <v>15</v>
+      </c>
+      <c r="C103">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L103" t="s">
+        <v>16</v>
+      </c>
+      <c r="N103" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14">
       <c r="A104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>103</v>
       </c>
-    </row>
-    <row r="105" spans="1:1">
+      <c r="B104" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L104" t="s">
+        <v>16</v>
+      </c>
+      <c r="N104" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
       <c r="A105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>104</v>
       </c>
-    </row>
-    <row r="106" spans="1:1">
+      <c r="B105" t="s">
+        <v>15</v>
+      </c>
+      <c r="C105">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L105" t="s">
+        <v>16</v>
+      </c>
+      <c r="N105" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14">
       <c r="A106">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>105</v>
       </c>
-    </row>
-    <row r="107" spans="1:1">
+      <c r="B106" t="s">
+        <v>15</v>
+      </c>
+      <c r="C106">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L106" t="s">
+        <v>16</v>
+      </c>
+      <c r="N106" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14">
       <c r="A107">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>106</v>
       </c>
-    </row>
-    <row r="108" spans="1:1">
+      <c r="B107" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L107" t="s">
+        <v>16</v>
+      </c>
+      <c r="N107" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14">
       <c r="A108">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>107</v>
       </c>
-    </row>
-    <row r="109" spans="1:1">
+      <c r="B108" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L108" t="s">
+        <v>16</v>
+      </c>
+      <c r="N108" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14">
       <c r="A109">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>108</v>
       </c>
-    </row>
-    <row r="110" spans="1:1">
+      <c r="B109" t="s">
+        <v>15</v>
+      </c>
+      <c r="C109">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L109" t="s">
+        <v>16</v>
+      </c>
+      <c r="N109" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14">
       <c r="A110">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>109</v>
       </c>
-    </row>
-    <row r="111" spans="1:1">
+      <c r="B110" t="s">
+        <v>15</v>
+      </c>
+      <c r="C110">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L110" t="s">
+        <v>16</v>
+      </c>
+      <c r="N110" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14">
       <c r="A111">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>110</v>
       </c>
-    </row>
-    <row r="112" spans="1:1">
+      <c r="B111" t="s">
+        <v>15</v>
+      </c>
+      <c r="C111">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L111" t="s">
+        <v>16</v>
+      </c>
+      <c r="N111" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14">
       <c r="A112">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>111</v>
       </c>
-    </row>
-    <row r="113" spans="1:1">
+      <c r="B112" t="s">
+        <v>15</v>
+      </c>
+      <c r="C112">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L112" t="s">
+        <v>16</v>
+      </c>
+      <c r="N112" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14">
       <c r="A113">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>112</v>
       </c>
-    </row>
-    <row r="114" spans="1:1">
+      <c r="B113" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L113" t="s">
+        <v>16</v>
+      </c>
+      <c r="N113" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14">
       <c r="A114">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>113</v>
       </c>
-    </row>
-    <row r="115" spans="1:1">
+      <c r="B114" t="s">
+        <v>15</v>
+      </c>
+      <c r="C114">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L114" t="s">
+        <v>16</v>
+      </c>
+      <c r="N114" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14">
       <c r="A115">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>114</v>
       </c>
-    </row>
-    <row r="116" spans="1:1">
+      <c r="B115" t="s">
+        <v>15</v>
+      </c>
+      <c r="C115">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L115" t="s">
+        <v>16</v>
+      </c>
+      <c r="N115" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14">
       <c r="A116">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>115</v>
       </c>
-    </row>
-    <row r="117" spans="1:1">
+      <c r="B116" t="s">
+        <v>15</v>
+      </c>
+      <c r="C116">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L116" t="s">
+        <v>16</v>
+      </c>
+      <c r="N116" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14">
       <c r="A117">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>116</v>
       </c>
-    </row>
-    <row r="118" spans="1:1">
+      <c r="B117" t="s">
+        <v>15</v>
+      </c>
+      <c r="C117">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L117" t="s">
+        <v>16</v>
+      </c>
+      <c r="N117" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14">
       <c r="A118">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>117</v>
       </c>
-    </row>
-    <row r="119" spans="1:1">
+      <c r="B118" t="s">
+        <v>15</v>
+      </c>
+      <c r="C118">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L118" t="s">
+        <v>16</v>
+      </c>
+      <c r="N118" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14">
       <c r="A119">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>118</v>
       </c>
-    </row>
-    <row r="120" spans="1:1">
+      <c r="B119" t="s">
+        <v>15</v>
+      </c>
+      <c r="C119">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L119" t="s">
+        <v>16</v>
+      </c>
+      <c r="N119" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14">
       <c r="A120">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>119</v>
       </c>
-    </row>
-    <row r="121" spans="1:1">
+      <c r="B120" t="s">
+        <v>15</v>
+      </c>
+      <c r="C120">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L120" t="s">
+        <v>16</v>
+      </c>
+      <c r="N120" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14">
       <c r="A121">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>120</v>
       </c>
-    </row>
-    <row r="122" spans="1:1">
+      <c r="B121" t="s">
+        <v>15</v>
+      </c>
+      <c r="C121">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L121" t="s">
+        <v>16</v>
+      </c>
+      <c r="N121" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14">
       <c r="A122">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>121</v>
       </c>
-    </row>
-    <row r="123" spans="1:1">
+      <c r="B122" t="s">
+        <v>15</v>
+      </c>
+      <c r="C122">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L122" t="s">
+        <v>16</v>
+      </c>
+      <c r="N122" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14">
       <c r="A123">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>122</v>
       </c>
-    </row>
-    <row r="124" spans="1:1">
+      <c r="B123" t="s">
+        <v>15</v>
+      </c>
+      <c r="C123">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L123" t="s">
+        <v>16</v>
+      </c>
+      <c r="N123" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14">
       <c r="A124">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>123</v>
       </c>
-    </row>
-    <row r="125" spans="1:1">
+      <c r="B124" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L124" t="s">
+        <v>16</v>
+      </c>
+      <c r="N124" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14">
       <c r="A125">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>124</v>
       </c>
-    </row>
-    <row r="126" spans="1:1">
+      <c r="B125" t="s">
+        <v>15</v>
+      </c>
+      <c r="C125">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L125" t="s">
+        <v>16</v>
+      </c>
+      <c r="N125" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14">
       <c r="A126">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>125</v>
       </c>
-    </row>
-    <row r="127" spans="1:1">
+      <c r="B126" t="s">
+        <v>15</v>
+      </c>
+      <c r="C126">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L126" t="s">
+        <v>16</v>
+      </c>
+      <c r="N126" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14">
       <c r="A127">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>126</v>
       </c>
-    </row>
-    <row r="128" spans="1:1">
+      <c r="B127" t="s">
+        <v>15</v>
+      </c>
+      <c r="C127">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L127" t="s">
+        <v>16</v>
+      </c>
+      <c r="N127" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14">
       <c r="A128">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>127</v>
       </c>
-    </row>
-    <row r="129" spans="1:1">
+      <c r="B128" t="s">
+        <v>15</v>
+      </c>
+      <c r="C128">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L128" t="s">
+        <v>16</v>
+      </c>
+      <c r="N128" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14">
       <c r="A129">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>128</v>
       </c>
-    </row>
-    <row r="130" spans="1:1">
+      <c r="B129" t="s">
+        <v>15</v>
+      </c>
+      <c r="C129">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L129" t="s">
+        <v>16</v>
+      </c>
+      <c r="N129" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14">
       <c r="A130">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>129</v>
       </c>
-    </row>
-    <row r="131" spans="1:1">
+      <c r="B130" t="s">
+        <v>15</v>
+      </c>
+      <c r="C130">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L130" t="s">
+        <v>16</v>
+      </c>
+      <c r="N130" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14">
       <c r="A131">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>130</v>
       </c>
-    </row>
-    <row r="132" spans="1:1">
+      <c r="B131" t="s">
+        <v>15</v>
+      </c>
+      <c r="C131">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L131" t="s">
+        <v>16</v>
+      </c>
+      <c r="N131" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14">
       <c r="A132">
-        <f t="shared" ref="A132:A188" si="2">A131+1</f>
+        <f t="shared" ref="A132:A188" si="8">A131+1</f>
         <v>131</v>
       </c>
-    </row>
-    <row r="133" spans="1:1">
+      <c r="B132" t="s">
+        <v>15</v>
+      </c>
+      <c r="C132">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L132" t="s">
+        <v>16</v>
+      </c>
+      <c r="N132" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14">
       <c r="A133">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>132</v>
       </c>
-    </row>
-    <row r="134" spans="1:1">
+      <c r="B133" t="s">
+        <v>15</v>
+      </c>
+      <c r="C133">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L133" t="s">
+        <v>16</v>
+      </c>
+      <c r="N133" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14">
       <c r="A134">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>133</v>
       </c>
-    </row>
-    <row r="135" spans="1:1">
+      <c r="B134" t="s">
+        <v>15</v>
+      </c>
+      <c r="C134">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L134" t="s">
+        <v>16</v>
+      </c>
+      <c r="N134" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14">
       <c r="A135">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>134</v>
       </c>
-    </row>
-    <row r="136" spans="1:1">
+      <c r="B135" t="s">
+        <v>15</v>
+      </c>
+      <c r="C135">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L135" t="s">
+        <v>16</v>
+      </c>
+      <c r="N135" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14">
       <c r="A136">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>135</v>
       </c>
-    </row>
-    <row r="137" spans="1:1">
+      <c r="B136" t="s">
+        <v>15</v>
+      </c>
+      <c r="C136">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L136" t="s">
+        <v>16</v>
+      </c>
+      <c r="N136" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14">
       <c r="A137">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>136</v>
       </c>
-    </row>
-    <row r="138" spans="1:1">
+      <c r="B137" t="s">
+        <v>15</v>
+      </c>
+      <c r="C137">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L137" t="s">
+        <v>16</v>
+      </c>
+      <c r="N137" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14">
       <c r="A138">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>137</v>
       </c>
-    </row>
-    <row r="139" spans="1:1">
+      <c r="B138" t="s">
+        <v>15</v>
+      </c>
+      <c r="C138">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L138" t="s">
+        <v>16</v>
+      </c>
+      <c r="N138" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14">
       <c r="A139">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>138</v>
       </c>
-    </row>
-    <row r="140" spans="1:1">
+      <c r="B139" t="s">
+        <v>15</v>
+      </c>
+      <c r="C139">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L139" t="s">
+        <v>16</v>
+      </c>
+      <c r="N139" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14">
       <c r="A140">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>139</v>
       </c>
-    </row>
-    <row r="141" spans="1:1">
+      <c r="B140" t="s">
+        <v>15</v>
+      </c>
+      <c r="C140">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L140" t="s">
+        <v>16</v>
+      </c>
+      <c r="N140" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14">
       <c r="A141">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>140</v>
       </c>
-    </row>
-    <row r="142" spans="1:1">
+      <c r="B141" t="s">
+        <v>15</v>
+      </c>
+      <c r="C141">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L141" t="s">
+        <v>16</v>
+      </c>
+      <c r="N141" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14">
       <c r="A142">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>141</v>
       </c>
-    </row>
-    <row r="143" spans="1:1">
+      <c r="B142" t="s">
+        <v>15</v>
+      </c>
+      <c r="C142">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="L142" t="s">
+        <v>16</v>
+      </c>
+      <c r="N142" t="str">
+        <f t="shared" si="7"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14">
       <c r="A143">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>142</v>
       </c>
-    </row>
-    <row r="144" spans="1:1">
+      <c r="B143" t="s">
+        <v>15</v>
+      </c>
+      <c r="C143">
+        <f t="shared" ref="C143:C176" si="9">C142</f>
+        <v>169</v>
+      </c>
+      <c r="L143" t="s">
+        <v>16</v>
+      </c>
+      <c r="N143" t="str">
+        <f t="shared" ref="N143:N176" si="10">N142</f>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14">
       <c r="A144">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>143</v>
       </c>
-    </row>
-    <row r="145" spans="1:1">
+      <c r="B144" t="s">
+        <v>15</v>
+      </c>
+      <c r="C144">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L144" t="s">
+        <v>16</v>
+      </c>
+      <c r="N144" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14">
       <c r="A145">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>144</v>
       </c>
-    </row>
-    <row r="146" spans="1:1">
+      <c r="B145" t="s">
+        <v>15</v>
+      </c>
+      <c r="C145">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L145" t="s">
+        <v>16</v>
+      </c>
+      <c r="N145" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14">
       <c r="A146">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>145</v>
       </c>
-    </row>
-    <row r="147" spans="1:1">
+      <c r="B146" t="s">
+        <v>15</v>
+      </c>
+      <c r="C146">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L146" t="s">
+        <v>16</v>
+      </c>
+      <c r="N146" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14">
       <c r="A147">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>146</v>
       </c>
-    </row>
-    <row r="148" spans="1:1">
+      <c r="B147" t="s">
+        <v>15</v>
+      </c>
+      <c r="C147">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L147" t="s">
+        <v>16</v>
+      </c>
+      <c r="N147" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14">
       <c r="A148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>147</v>
       </c>
-    </row>
-    <row r="149" spans="1:1">
+      <c r="B148" t="s">
+        <v>15</v>
+      </c>
+      <c r="C148">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L148" t="s">
+        <v>16</v>
+      </c>
+      <c r="N148" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14">
       <c r="A149">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>148</v>
       </c>
-    </row>
-    <row r="150" spans="1:1">
+      <c r="B149" t="s">
+        <v>15</v>
+      </c>
+      <c r="C149">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L149" t="s">
+        <v>16</v>
+      </c>
+      <c r="N149" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14">
       <c r="A150">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>149</v>
       </c>
-    </row>
-    <row r="151" spans="1:1">
+      <c r="B150" t="s">
+        <v>15</v>
+      </c>
+      <c r="C150">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L150" t="s">
+        <v>16</v>
+      </c>
+      <c r="N150" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14">
       <c r="A151">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>150</v>
       </c>
-    </row>
-    <row r="152" spans="1:1">
+      <c r="B151" t="s">
+        <v>15</v>
+      </c>
+      <c r="C151">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L151" t="s">
+        <v>16</v>
+      </c>
+      <c r="N151" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14">
       <c r="A152">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>151</v>
       </c>
-    </row>
-    <row r="153" spans="1:1">
+      <c r="B152" t="s">
+        <v>15</v>
+      </c>
+      <c r="C152">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L152" t="s">
+        <v>16</v>
+      </c>
+      <c r="N152" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14">
       <c r="A153">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>152</v>
       </c>
-    </row>
-    <row r="154" spans="1:1">
+      <c r="B153" t="s">
+        <v>15</v>
+      </c>
+      <c r="C153">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L153" t="s">
+        <v>16</v>
+      </c>
+      <c r="N153" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14">
       <c r="A154">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>153</v>
       </c>
-    </row>
-    <row r="155" spans="1:1">
+      <c r="B154" t="s">
+        <v>15</v>
+      </c>
+      <c r="C154">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L154" t="s">
+        <v>16</v>
+      </c>
+      <c r="N154" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14">
       <c r="A155">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>154</v>
       </c>
-    </row>
-    <row r="156" spans="1:1">
+      <c r="B155" t="s">
+        <v>15</v>
+      </c>
+      <c r="C155">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L155" t="s">
+        <v>16</v>
+      </c>
+      <c r="N155" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14">
       <c r="A156">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>155</v>
       </c>
-    </row>
-    <row r="157" spans="1:1">
+      <c r="B156" t="s">
+        <v>15</v>
+      </c>
+      <c r="C156">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L156" t="s">
+        <v>16</v>
+      </c>
+      <c r="N156" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14">
       <c r="A157">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>156</v>
       </c>
-    </row>
-    <row r="158" spans="1:1">
+      <c r="B157" t="s">
+        <v>15</v>
+      </c>
+      <c r="C157">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L157" t="s">
+        <v>16</v>
+      </c>
+      <c r="N157" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14">
       <c r="A158">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>157</v>
       </c>
-    </row>
-    <row r="159" spans="1:1">
+      <c r="B158" t="s">
+        <v>15</v>
+      </c>
+      <c r="C158">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L158" t="s">
+        <v>16</v>
+      </c>
+      <c r="N158" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14">
       <c r="A159">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>158</v>
       </c>
-    </row>
-    <row r="160" spans="1:1">
+      <c r="B159" t="s">
+        <v>15</v>
+      </c>
+      <c r="C159">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L159" t="s">
+        <v>16</v>
+      </c>
+      <c r="N159" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14">
       <c r="A160">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>159</v>
       </c>
-    </row>
-    <row r="161" spans="1:1">
+      <c r="B160" t="s">
+        <v>15</v>
+      </c>
+      <c r="C160">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L160" t="s">
+        <v>16</v>
+      </c>
+      <c r="N160" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14">
       <c r="A161">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>160</v>
       </c>
-    </row>
-    <row r="162" spans="1:1">
+      <c r="B161" t="s">
+        <v>15</v>
+      </c>
+      <c r="C161">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L161" t="s">
+        <v>16</v>
+      </c>
+      <c r="N161" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14">
       <c r="A162">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>161</v>
       </c>
-    </row>
-    <row r="163" spans="1:1">
+      <c r="B162" t="s">
+        <v>15</v>
+      </c>
+      <c r="C162">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L162" t="s">
+        <v>16</v>
+      </c>
+      <c r="N162" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14">
       <c r="A163">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>162</v>
       </c>
-    </row>
-    <row r="164" spans="1:1">
+      <c r="B163" t="s">
+        <v>15</v>
+      </c>
+      <c r="C163">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L163" t="s">
+        <v>16</v>
+      </c>
+      <c r="N163" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14">
       <c r="A164">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>163</v>
       </c>
-    </row>
-    <row r="165" spans="1:1">
+      <c r="B164" t="s">
+        <v>15</v>
+      </c>
+      <c r="C164">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L164" t="s">
+        <v>16</v>
+      </c>
+      <c r="N164" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14">
       <c r="A165">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>164</v>
       </c>
-    </row>
-    <row r="166" spans="1:1">
+      <c r="B165" t="s">
+        <v>15</v>
+      </c>
+      <c r="C165">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L165" t="s">
+        <v>16</v>
+      </c>
+      <c r="N165" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14">
       <c r="A166">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>165</v>
       </c>
-    </row>
-    <row r="167" spans="1:1">
+      <c r="B166" t="s">
+        <v>15</v>
+      </c>
+      <c r="C166">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L166" t="s">
+        <v>16</v>
+      </c>
+      <c r="N166" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14">
       <c r="A167">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>166</v>
       </c>
-    </row>
-    <row r="168" spans="1:1">
+      <c r="B167" t="s">
+        <v>15</v>
+      </c>
+      <c r="C167">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L167" t="s">
+        <v>16</v>
+      </c>
+      <c r="N167" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14">
       <c r="A168">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>167</v>
       </c>
-    </row>
-    <row r="169" spans="1:1">
+      <c r="B168" t="s">
+        <v>15</v>
+      </c>
+      <c r="C168">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L168" t="s">
+        <v>16</v>
+      </c>
+      <c r="N168" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14">
       <c r="A169">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>168</v>
       </c>
-    </row>
-    <row r="170" spans="1:1">
+      <c r="B169" t="s">
+        <v>15</v>
+      </c>
+      <c r="C169">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L169" t="s">
+        <v>16</v>
+      </c>
+      <c r="N169" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14">
       <c r="A170">
-        <f t="shared" si="2"/>
-        <v>169</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1">
+        <f t="shared" si="8"/>
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
+        <v>15</v>
+      </c>
+      <c r="C170">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L170" t="s">
+        <v>16</v>
+      </c>
+      <c r="N170" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14">
       <c r="A171">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>170</v>
       </c>
-    </row>
-    <row r="172" spans="1:1">
+      <c r="B171" t="s">
+        <v>15</v>
+      </c>
+      <c r="C171">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L171" t="s">
+        <v>16</v>
+      </c>
+      <c r="N171" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14">
       <c r="A172">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>171</v>
       </c>
-    </row>
-    <row r="173" spans="1:1">
+      <c r="B172" t="s">
+        <v>15</v>
+      </c>
+      <c r="C172">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L172" t="s">
+        <v>16</v>
+      </c>
+      <c r="N172" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14">
       <c r="A173">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>172</v>
       </c>
-    </row>
-    <row r="174" spans="1:1">
+      <c r="B173" t="s">
+        <v>15</v>
+      </c>
+      <c r="C173">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L173" t="s">
+        <v>16</v>
+      </c>
+      <c r="N173" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14">
       <c r="A174">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>173</v>
       </c>
-    </row>
-    <row r="175" spans="1:1">
+      <c r="B174" t="s">
+        <v>15</v>
+      </c>
+      <c r="C174">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L174" t="s">
+        <v>16</v>
+      </c>
+      <c r="N174" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14">
       <c r="A175">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>174</v>
       </c>
-    </row>
-    <row r="176" spans="1:1">
+      <c r="B175" t="s">
+        <v>15</v>
+      </c>
+      <c r="C175">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L175" t="s">
+        <v>16</v>
+      </c>
+      <c r="N175" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14">
       <c r="A176">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>175</v>
       </c>
-    </row>
-    <row r="177" spans="1:1">
+      <c r="B176" t="s">
+        <v>15</v>
+      </c>
+      <c r="C176">
+        <f t="shared" si="9"/>
+        <v>169</v>
+      </c>
+      <c r="L176" t="s">
+        <v>16</v>
+      </c>
+      <c r="N176" t="str">
+        <f t="shared" si="10"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14">
       <c r="A177">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>176</v>
       </c>
-    </row>
-    <row r="178" spans="1:1">
+      <c r="B177" t="s">
+        <v>15</v>
+      </c>
+      <c r="C177">
+        <v>170</v>
+      </c>
+      <c r="L177" t="s">
+        <v>16</v>
+      </c>
+      <c r="N177" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14">
       <c r="A178">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>177</v>
       </c>
-    </row>
-    <row r="179" spans="1:1">
+      <c r="B178" t="s">
+        <v>15</v>
+      </c>
+      <c r="C178">
+        <f>C177</f>
+        <v>170</v>
+      </c>
+      <c r="L178" t="s">
+        <v>16</v>
+      </c>
+      <c r="N178" t="str">
+        <f>N177</f>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 170</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14">
       <c r="A179">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>178</v>
       </c>
-    </row>
-    <row r="180" spans="1:1">
+      <c r="B179" t="s">
+        <v>15</v>
+      </c>
+      <c r="C179">
+        <f t="shared" ref="C179:C188" si="11">C178</f>
+        <v>170</v>
+      </c>
+      <c r="L179" t="s">
+        <v>16</v>
+      </c>
+      <c r="N179" t="str">
+        <f t="shared" ref="N179:N188" si="12">N178</f>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 170</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14">
       <c r="A180">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>179</v>
       </c>
-    </row>
-    <row r="181" spans="1:1">
+      <c r="B180" t="s">
+        <v>15</v>
+      </c>
+      <c r="C180">
+        <f t="shared" si="11"/>
+        <v>170</v>
+      </c>
+      <c r="L180" t="s">
+        <v>16</v>
+      </c>
+      <c r="N180" t="str">
+        <f t="shared" si="12"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 170</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14">
       <c r="A181">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>180</v>
       </c>
-    </row>
-    <row r="182" spans="1:1">
+      <c r="B181" t="s">
+        <v>15</v>
+      </c>
+      <c r="C181">
+        <f t="shared" si="11"/>
+        <v>170</v>
+      </c>
+      <c r="L181" t="s">
+        <v>16</v>
+      </c>
+      <c r="N181" t="str">
+        <f t="shared" si="12"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 170</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14">
       <c r="A182">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>181</v>
       </c>
-    </row>
-    <row r="183" spans="1:1">
+      <c r="B182" t="s">
+        <v>15</v>
+      </c>
+      <c r="C182">
+        <f t="shared" si="11"/>
+        <v>170</v>
+      </c>
+      <c r="L182" t="s">
+        <v>16</v>
+      </c>
+      <c r="N182" t="str">
+        <f t="shared" si="12"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 170</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14">
       <c r="A183">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>182</v>
       </c>
-    </row>
-    <row r="184" spans="1:1">
+      <c r="B183" t="s">
+        <v>15</v>
+      </c>
+      <c r="C183">
+        <f t="shared" si="11"/>
+        <v>170</v>
+      </c>
+      <c r="L183" t="s">
+        <v>16</v>
+      </c>
+      <c r="N183" t="str">
+        <f t="shared" si="12"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 170</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14">
       <c r="A184">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>183</v>
       </c>
-    </row>
-    <row r="185" spans="1:1">
+      <c r="B184" t="s">
+        <v>15</v>
+      </c>
+      <c r="C184">
+        <f t="shared" si="11"/>
+        <v>170</v>
+      </c>
+      <c r="L184" t="s">
+        <v>16</v>
+      </c>
+      <c r="N184" t="str">
+        <f t="shared" si="12"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 170</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14">
       <c r="A185">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>184</v>
       </c>
-    </row>
-    <row r="186" spans="1:1">
+      <c r="B185" t="s">
+        <v>15</v>
+      </c>
+      <c r="C185">
+        <f t="shared" si="11"/>
+        <v>170</v>
+      </c>
+      <c r="L185" t="s">
+        <v>16</v>
+      </c>
+      <c r="N185" t="str">
+        <f t="shared" si="12"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 170</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14">
       <c r="A186">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>185</v>
       </c>
-    </row>
-    <row r="187" spans="1:1">
+      <c r="B186" t="s">
+        <v>15</v>
+      </c>
+      <c r="C186">
+        <f t="shared" si="11"/>
+        <v>170</v>
+      </c>
+      <c r="L186" t="s">
+        <v>16</v>
+      </c>
+      <c r="N186" t="str">
+        <f t="shared" si="12"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 170</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14">
       <c r="A187">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>186</v>
       </c>
-    </row>
-    <row r="188" spans="1:1">
+      <c r="B187" t="s">
+        <v>15</v>
+      </c>
+      <c r="C187">
+        <f t="shared" si="11"/>
+        <v>170</v>
+      </c>
+      <c r="L187" t="s">
+        <v>16</v>
+      </c>
+      <c r="N187" t="str">
+        <f t="shared" si="12"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 170</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14">
       <c r="A188">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>187</v>
+      </c>
+      <c r="B188" t="s">
+        <v>15</v>
+      </c>
+      <c r="C188">
+        <f t="shared" si="11"/>
+        <v>170</v>
+      </c>
+      <c r="L188" t="s">
+        <v>16</v>
+      </c>
+      <c r="N188" t="str">
+        <f t="shared" si="12"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 170</v>
       </c>
     </row>
   </sheetData>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Minor.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Minor.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="22">
   <si>
     <t>ID</t>
   </si>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t>Dawes Rolls Full Document - Choctaw By Blood - Page 170</t>
+  </si>
+  <si>
+    <t>Image Name</t>
+  </si>
+  <si>
+    <t>Image Binary</t>
   </si>
 </sst>
 </file>
@@ -405,15 +411,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O188"/>
+  <dimension ref="A1:Q188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="12" max="12" width="24.85546875" customWidth="1"/>
     <col min="14" max="14" width="57.140625" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" customWidth="1"/>
+    <col min="17" max="17" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -459,8 +467,14 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
@@ -477,7 +491,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -497,7 +511,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:17">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -517,7 +531,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:17">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -537,7 +551,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -557,7 +571,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:17">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -577,7 +591,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -597,7 +611,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -617,7 +631,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:17">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -637,7 +651,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -657,7 +671,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:17">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -677,7 +691,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:17">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -695,7 +709,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:17">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -715,7 +729,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:17">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -735,7 +749,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:17">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Minor.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Minor.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="23">
   <si>
     <t>ID</t>
   </si>
@@ -76,10 +76,13 @@
     <t>Dawes Rolls Full Document - Choctaw By Blood - Page 170</t>
   </si>
   <si>
-    <t>Image Name</t>
+    <t>ImageName</t>
   </si>
   <si>
-    <t>Image Binary</t>
+    <t>ImageBinary</t>
+  </si>
+  <si>
+    <t>TribeRelationship</t>
   </si>
 </sst>
 </file>
@@ -411,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q188"/>
+  <dimension ref="A1:R188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -419,9 +422,10 @@
     <col min="14" max="14" width="57.140625" customWidth="1"/>
     <col min="16" max="16" width="13.28515625" customWidth="1"/>
     <col min="17" max="17" width="17" customWidth="1"/>
+    <col min="18" max="18" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -473,8 +477,11 @@
       <c r="Q1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -491,7 +498,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -511,7 +518,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -531,7 +538,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -551,7 +558,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -571,7 +578,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -591,7 +598,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -611,7 +618,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -631,7 +638,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -651,7 +658,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -671,7 +678,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -691,7 +698,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -709,7 +716,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -729,7 +736,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -749,7 +756,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 169</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
